--- a/build/simple-flow/SimpleFlow_Bugs-for-Milos-Confirm.xlsx
+++ b/build/simple-flow/SimpleFlow_Bugs-for-Milos-Confirm.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -532,12 +532,12 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>A mechanic finishes a repair job. Right now, that same mechanic is also allowed to be the person who double-checks and approves their own work - nobody else has to look it over. Picture one person doing the repair AND signing off that it's all correct.</t>
+          <t>The screen correctly hides the "finish" and "approve" buttons from people who aren't supposed to have them. But the system behind the screen doesn't fully block those actions - so a very technical person could still find a way around the screen to do them.</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>The person who did the work can approve their own work. No second person is needed to review it.</t>
+          <t>The buttons are hidden from the right people on screen, but the block isn't fully enforced behind the scenes.</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -549,7 +549,7 @@
         <is>
           <t>A) This is a problem - please fix it.
 B) This is fine - it's how it should work.
-C) Let each shop choose whether a different person must approve.</t>
+C) Fine for now, but fix it later.</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr"/>
@@ -560,12 +560,12 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>The screen correctly hides the "finish" and "approve" buttons from people who aren't supposed to have them. But the system behind the screen doesn't fully block those actions - so a very technical person could still find a way around the screen to do them.</t>
+          <t>When finishing a repair job, the screen asks for details like the mileage, the vehicle's ID number, or the engine hours. But the system behind the screen doesn't truly require them - so a very technical person could skip those details by going around the screen.</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>The buttons are hidden from the right people on screen, but the block isn't fully enforced behind the scenes.</t>
+          <t>The screen asks for those details, but they aren't truly required behind the scenes and could be skipped.</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -588,12 +588,12 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>When finishing a repair job, the screen asks for details like the mileage, the vehicle's ID number, or the engine hours. But the system behind the screen doesn't truly require them - so a very technical person could skip those details by going around the screen.</t>
+          <t>There are two ways to receive parts that have arrived from a supplier. The newer way works fine. The older way shows an error message when a parts person tries to use it for parts that came from a repair job.</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>The screen asks for those details, but they aren't truly required behind the scenes and could be skipped.</t>
+          <t>The newer receiving screen works. The older receiving screen shows an error for these parts, so people should use the newer one.</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -605,7 +605,7 @@
         <is>
           <t>A) This is a problem - please fix it.
 B) This is fine - it's how it should work.
-C) Fine for now, but fix it later.</t>
+C) Fine to just retire the old screen and keep the new one.</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr"/>
@@ -616,12 +616,12 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>There are two ways to receive parts that have arrived from a supplier. The newer way works fine. The older way shows an error message when a parts person tries to use it for parts that came from a repair job.</t>
+          <t>When a brand-new shop opens the app for the very first time, some of the starting switches are set the wrong way by default - for example, jobs auto-approve on their own, and a supplier's bill isn't required when it should be.</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>The newer receiving screen works. The older receiving screen shows an error for these parts, so people should use the newer one.</t>
+          <t>A brand-new shop starts with those switches set the opposite way from what was agreed (auto-approve on, supplier's bill not required).</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -630,40 +630,12 @@
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>A) This is a problem - please fix it.
-B) This is fine - it's how it should work.
-C) Fine to just retire the old screen and keep the new one.</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr"/>
-    </row>
-    <row r="9" ht="150" customHeight="1">
-      <c r="A9" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>When a brand-new shop opens the app for the very first time, some of the starting switches are set the wrong way by default - for example, jobs auto-approve on their own, and a supplier's bill isn't required when it should be.</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>A brand-new shop starts with those switches set the opposite way from what was agreed (auto-approve on, supplier's bill not required).</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>Is this a problem we should fix, or is this how it should work?</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>A) This is a problem - please fix it.
 B) This is fine - it's how it should work.</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr"/>
+      <c r="F8" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -680,7 +652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -748,63 +720,20 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>BUG-5</t>
+          <t>BUG-6 + BUG-7</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>TICKET 1</t>
+          <t>TICKET 2</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>SF-PERM-08  C29412  https://shopview.testrail.io/index.php?/cases/view/29412
-SF-PERM-04  C29408  https://shopview.testrail.io/index.php?/cases/view/29408
-SF-PERM-07  C29411  https://shopview.testrail.io/index.php?/cases/view/29411
-SF-REV-09  C29394  https://shopview.testrail.io/index.php?/cases/view/29394</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>SV-8183 reviewer!=completer rule (the one net-new Simple-Flow permission). requirements.md Story 16.</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>NOT filed (Atlassian MCP unavailable at run time). Reproduced live: admin sent WO S2-15752 to review then same admin confirmed it. Evidence viu-evidence/REV-admin-completer-markreviewed.png.</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>A (problem) -&gt; file TICKET 1 (High); SF-PERM-08 stays Failed/Deviation and the reviewer!=completer negative is enforced. B (fine) -&gt; mark SF-PERM-08 + related expected/pass (self-review allowed by design); drop the ticket. C -&gt; make it a per-shop setting (new requirement + spec/story update).</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="120" customHeight="1">
-      <c r="A5" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>BUG-6 + BUG-7</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>TICKET 2</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>SF-PERM-06  C29410  https://shopview.testrail.io/index.php?/cases/view/29410
 SF-PERM-02  C29406  https://shopview.testrail.io/index.php?/cases/view/29406
@@ -812,42 +741,42 @@
 SF-REV-09  C29394  https://shopview.testrail.io/index.php?/cases/view/29394</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>SV-8183 backend-enforcement claim vs SV-7864 atom-collapse. Milos Round-2 Q5 already ruled UI gating = v1 pass; this tracks the backend gap.</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>NOT filed. UI gating passes; backend allows the action (201) via API for a role without the permission (e.g. Technician). Recorded 'UI pass / API fail'.</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>A (problem) -&gt; file TICKET 2 (Medium) to add backend enforcement; keep cases 'UI pass / API fail'. B (fine) -&gt; accept UI-only gating as intended (atom-collapse per SV-7864); mark cases pass on UI, drop ticket. C -&gt; file but defer (backlog).</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="132" customHeight="1">
-      <c r="A6" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
+    <row r="5" ht="132" customHeight="1">
+      <c r="A5" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>BUG-8</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>TICKET 3</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>SF-VAL-01  C29415  https://shopview.testrail.io/index.php?/cases/view/29415
 SF-VAL-02  C29416  https://shopview.testrail.io/index.php?/cases/view/29416
@@ -857,42 +786,42 @@
 SF-REV-03  C29388  https://shopview.testrail.io/index.php?/cases/view/29388</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>SV-8183 backend-enforcement claim; requirements.md §4 required-vehicle-field gates (mileage / VIN / engine hours). Related SV-7864 atom-collapse.</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>NOT filed. Wizard blocks completion until fields are filled (viu-evidence/VIU2-02-mileage-gate.png) but backend completes without them (simple-complete returned 201 with mileage empty).</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>A (problem) -&gt; file TICKET 3 (Medium) to enforce required fields backend-side; cases stay Deviation until fixed. B (fine) -&gt; UI-only enforcement accepted; mark SF-VAL-01/02/03 + related expected/pass on UI. C -&gt; file but defer.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="374" customHeight="1">
-      <c r="A7" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
+    <row r="6" ht="374" customHeight="1">
+      <c r="A6" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>BUG-11</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>TICKET 4</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>SF-COMP-13  C29302  https://shopview.testrail.io/index.php?/cases/view/29302
 SF-COMP-19  C29308  https://shopview.testrail.io/index.php?/cases/view/29308
@@ -913,72 +842,72 @@
 SF-CORE-07  C29319  https://shopview.testrail.io/index.php?/cases/view/29319</t>
         </is>
       </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>SV-7301 Story 10 (receive creates/links part) / Story 8 (Bulk Receive = the working path). Downgraded to Low 2026-07-09: the 500 is confined to the LEGACY single-PO Accept-Delivery path; Bulk Receive works (200).</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>NOT filed. Legacy Accept-Delivery receive of a WO-PO returns HTTP 500; new Bulk Receive receives the same WO PO fine. Evidence R7-01/R7-04/R7-06 in viu-evidence/. Affected cases now largely testable via Bulk Receive.</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>A (problem) -&gt; file TICKET 4 (Low) to fix the legacy Accept-Delivery 500. B (fine) -&gt; accept legacy path as-is (use Bulk Receive); mark cases pass via Bulk Receive path. C -&gt; retire the legacy single-PO Accept-Delivery surface (product/scope decision) and standardize on Bulk Receive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="120" customHeight="1">
+      <c r="A7" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>GAP-B</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>TICKET 5</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>SF-SET-08  C29282  https://shopview.testrail.io/index.php?/cases/view/29282</t>
+        </is>
+      </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>SV-7301 Story 10 (receive creates/links part) / Story 8 (Bulk Receive = the working path). Downgraded to Low 2026-07-09: the 500 is confined to the LEGACY single-PO Accept-Delivery path; Bulk Receive works (200).</t>
+          <t>SV-7301 §4 / Story 1 first-use defaults (confirmed Milos Q3: Auto-approve Lines OFF, Create Purchase Orders ON, Vendor Invoice REQUIRED).</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>NOT filed. Legacy Accept-Delivery receive of a WO-PO returns HTTP 500; new Bulk Receive receives the same WO PO fine. Evidence R7-01/R7-04/R7-06 in viu-evidence/. Affected cases now largely testable via Bulk Receive.</t>
+          <t>NOT filed. First-use build ships Auto-approve Lines ON and Vendor Invoice Optional (autoApproveLines:true, requireVendorInvoiceNumber:false) - opposite of the confirmed defaults.</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>A (problem) -&gt; file TICKET 4 (Low) to fix the legacy Accept-Delivery 500. B (fine) -&gt; accept legacy path as-is (use Bulk Receive); mark cases pass via Bulk Receive path. C -&gt; retire the legacy single-PO Accept-Delivery surface (product/scope decision) and standardize on Bulk Receive.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="120" customHeight="1">
-      <c r="A8" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>GAP-B</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>TICKET 5</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>SF-SET-08  C29282  https://shopview.testrail.io/index.php?/cases/view/29282</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>SV-7301 §4 / Story 1 first-use defaults (confirmed Milos Q3: Auto-approve Lines OFF, Create Purchase Orders ON, Vendor Invoice REQUIRED).</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>NOT filed. First-use build ships Auto-approve Lines ON and Vendor Invoice Optional (autoApproveLines:true, requireVendorInvoiceNumber:false) - opposite of the confirmed defaults.</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
           <t>A (problem) -&gt; file TICKET 5 (Medium) to correct the first-use defaults; SF-SET-08 stays Deviation until fixed. B (fine) -&gt; Milos re-confirms the shipped defaults are acceptable; update SF-SET-08 expected to match live and pass.</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="90" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Notes: The 5 items are the reconciled Simple Flow bug drafts (jira-bug-drafts.md, 2026-07-09 post-Milos-Round-2). This sheet is the PO-DECISION view so Milos can confirm expected-vs-bug; it does NOT replace the QA/dev-facing SimpleFlow_Bug-Drafts.xlsx. TestRail Case IDs sourced from testrail-id-map.csv (standing rule 8); every affected case's clickable link is preserved in the .md mirror. Bugs stay OUT of the PO-facing tab (standing rule 7) - it only asks the product decision. None of the 5 are filed in Jira yet (Atlassian MCP was unavailable at run time).</t>
+    <row r="9" ht="90" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Notes: These items are the reconciled Simple Flow bug drafts (jira-bug-drafts.md, 2026-07-09 post-Milos-Round-2, updated 2026-07-10). BUG-5/TICKET 1 (reviewer can sign off own WO) was DROPPED 2026-07-10 as expected behavior per Milos and is no longer listed. This sheet is the PO-DECISION view so Milos can confirm expected-vs-bug; it does NOT replace the QA/dev-facing SimpleFlow_Bug-Drafts.xlsx. TestRail Case IDs sourced from testrail-id-map.csv (standing rule 8); every affected case's clickable link is preserved in the .md mirror. Bugs stay OUT of the PO-facing tab (standing rule 7) - it only asks the product decision. None of the 5 are filed in Jira yet (Atlassian MCP was unavailable at run time).</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A9:H9"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <hyperlinks>
@@ -986,7 +915,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
